--- a/CPBWorkbook.xlsx
+++ b/CPBWorkbook.xlsx
@@ -2305,7 +2305,7 @@
     <t>Verify M365 licensing eligibility</t>
   </si>
   <si>
-    <t>Customer must have M365 Business Basic, Standard, or Premium. Confirm Copilot Business ($21/user/mo) or M365 Copilot add-on licenses are in scope. Check update channel (Current or Monthly Enterprise).</t>
+    <t xml:space="preserve">Customer must have M365 Business Basic, Standard, or Premium. Confirm Copilot Business licensing in scope: $18/user/mo standalone (promo through Dec 2026) or bundled at $21–23.50/user/mo via M365 Business Basic/Standard with Copilot (GA since Jul 1, 2026), or M365 Copilot add-on licenses. Check update channel (Current or Monthly Enterprise).</t>
   </si>
   <si>
     <t>AI Specialist / L3</t>
@@ -2647,7 +2647,7 @@
     <t>Define 12-month AI roadmap with customer</t>
   </si>
   <si>
-    <t>Tier 1 → Tier 2 progression path. Identify 1–2 agent build candidates. Note upcoming M365 releases (Copilot Cowork in-scope for Frontier partners). Set next 90-day goals.</t>
+    <t xml:space="preserve">Tier 1 → Tier 2 progression path. Identify 1–2 agent build candidates. Cowork is GA (since Jun 16, 2026) on usage-based billing — flag its Copilot Credits consumption model as a cost-governance conversation, not an upcoming release. Set next 90-day goals.</t>
   </si>
   <si>
     <t>Submit MCI reimbursement application (if eligible)</t>
